--- a/worklog/v2.2.3/s10/pjm/v3/test/ods_tech_state_measure_v2.xlsx
+++ b/worklog/v2.2.3/s10/pjm/v3/test/ods_tech_state_measure_v2.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="225">
   <si>
     <t>项目编号</t>
   </si>
@@ -538,169 +538,151 @@
     <t>试验方案已编制完成</t>
   </si>
   <si>
+    <t>PJ-2025-006</t>
+  </si>
+  <si>
+    <t>钱海</t>
+  </si>
+  <si>
     <t>PJ-2025-008</t>
   </si>
   <si>
+    <t>赵敏</t>
+  </si>
+  <si>
     <t>PJ-2025-005</t>
   </si>
   <si>
-    <t>2025年03月15日</t>
-  </si>
-  <si>
-    <t>2025-4-10</t>
+    <t>2025/3/5</t>
+  </si>
+  <si>
+    <t>孙伟</t>
+  </si>
+  <si>
+    <t>2025年03月20日</t>
+  </si>
+  <si>
+    <t>PJ-2025-007</t>
+  </si>
+  <si>
+    <t>待定</t>
+  </si>
+  <si>
+    <t>王鹏</t>
+  </si>
+  <si>
+    <t>郭伟</t>
+  </si>
+  <si>
+    <t>2025年3月15日</t>
+  </si>
+  <si>
+    <t>PJ-2025-003</t>
+  </si>
+  <si>
+    <t>2025年02月05日</t>
+  </si>
+  <si>
+    <t>2025年4月5日</t>
+  </si>
+  <si>
+    <t>2025/03/20</t>
+  </si>
+  <si>
+    <t>2025年04月09日</t>
+  </si>
+  <si>
+    <t>2025年03月30日</t>
+  </si>
+  <si>
+    <t>2025-02-30</t>
+  </si>
+  <si>
+    <t>2025-4-5</t>
+  </si>
+  <si>
+    <t>黄磊</t>
+  </si>
+  <si>
+    <t>PJ-2025-004</t>
+  </si>
+  <si>
+    <t>未知</t>
+  </si>
+  <si>
+    <t>2025年04月10日</t>
+  </si>
+  <si>
+    <t>2025-13-05</t>
+  </si>
+  <si>
+    <t>2025-03-32</t>
   </si>
   <si>
     <t>李雪</t>
   </si>
   <si>
-    <t>PJ-2025-007</t>
-  </si>
-  <si>
-    <t>2025年2月5日</t>
-  </si>
-  <si>
-    <t>待定</t>
-  </si>
-  <si>
-    <t>2025-04-32</t>
-  </si>
-  <si>
-    <t>PJ-2025-003</t>
-  </si>
-  <si>
-    <t>郭伟</t>
-  </si>
-  <si>
-    <t>未知</t>
-  </si>
-  <si>
-    <t>2025.3.25</t>
+    <t>20205/03/15</t>
+  </si>
+  <si>
+    <t>2025-03</t>
+  </si>
+  <si>
+    <t>2025-02</t>
+  </si>
+  <si>
+    <t>2025-13-15</t>
   </si>
   <si>
     <t>秦川</t>
   </si>
   <si>
-    <t>PJ-2025-006</t>
-  </si>
-  <si>
-    <t>PJ-2025-004</t>
-  </si>
-  <si>
-    <t>2025/4/1</t>
-  </si>
-  <si>
-    <t>2025年2月28日</t>
-  </si>
-  <si>
-    <t>2025-13-01</t>
-  </si>
-  <si>
-    <t>2025年2月15日</t>
-  </si>
-  <si>
-    <t>20205/03/01</t>
-  </si>
-  <si>
-    <t>黄磊</t>
-  </si>
-  <si>
-    <t>王鹏</t>
-  </si>
-  <si>
-    <t>2025.3.15</t>
-  </si>
-  <si>
-    <t>2025/04/05</t>
+    <t>2025/04/10</t>
+  </si>
+  <si>
+    <t>20205/04/01</t>
+  </si>
+  <si>
+    <t>2025年3月20日</t>
+  </si>
+  <si>
+    <t>20205/03/25</t>
+  </si>
+  <si>
+    <t>2025/04/01</t>
   </si>
   <si>
     <t>TBD</t>
   </si>
   <si>
-    <t>孙伟</t>
-  </si>
-  <si>
-    <t>2025-01-32</t>
-  </si>
-  <si>
-    <t>2025-4-15</t>
-  </si>
-  <si>
-    <t>2025/4/10</t>
-  </si>
-  <si>
-    <t>2025年4月1日</t>
-  </si>
-  <si>
-    <t>2025-04</t>
-  </si>
-  <si>
-    <t>2025-03</t>
-  </si>
-  <si>
-    <t>2025年04月05日</t>
-  </si>
-  <si>
-    <t>2025.4.9</t>
-  </si>
-  <si>
-    <t>20250/03/15</t>
-  </si>
-  <si>
-    <t>2025/03/30</t>
-  </si>
-  <si>
-    <t>20205/01/20</t>
-  </si>
-  <si>
-    <t>2025-02-30</t>
-  </si>
-  <si>
-    <t>赵敏</t>
-  </si>
-  <si>
-    <t>2025年4月10日</t>
-  </si>
-  <si>
-    <t>2025-01</t>
-  </si>
-  <si>
-    <t>20205/03/15</t>
-  </si>
-  <si>
-    <t>2025.2.5</t>
-  </si>
-  <si>
-    <t>2025年03月20日</t>
-  </si>
-  <si>
-    <t>2025.4.1</t>
-  </si>
-  <si>
-    <t>20250/05/01</t>
-  </si>
-  <si>
-    <t>2025-3-15</t>
-  </si>
-  <si>
-    <t>2025/3/5</t>
-  </si>
-  <si>
-    <t>2025/04/02</t>
-  </si>
-  <si>
-    <t>20250/03/05</t>
-  </si>
-  <si>
-    <t>2025/03/22</t>
-  </si>
-  <si>
-    <t>2025-3-25</t>
-  </si>
-  <si>
-    <t>钱海</t>
-  </si>
-  <si>
-    <t>2025-05-32</t>
+    <t>2025-13-28</t>
+  </si>
+  <si>
+    <t>2025.3.5</t>
+  </si>
+  <si>
+    <t>20250/04/05</t>
+  </si>
+  <si>
+    <t>2025-13-20</t>
+  </si>
+  <si>
+    <t>20205/04/10</t>
+  </si>
+  <si>
+    <t>20250/02/05</t>
+  </si>
+  <si>
+    <t>2025-4-1</t>
+  </si>
+  <si>
+    <t>2025.5.15</t>
+  </si>
+  <si>
+    <t>20250/02/28</t>
+  </si>
+  <si>
+    <t>20250/04/09</t>
   </si>
 </sst>
 </file>
@@ -1955,12 +1937,12 @@
         <v>73</v>
       </c>
       <c r="AO10" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B11" t="s">
         <v>42</v>
@@ -1999,7 +1981,7 @@
         <v>53</v>
       </c>
       <c r="N11" t="s">
-        <v>178</v>
+        <v>54</v>
       </c>
       <c r="O11" t="s">
         <v>55</v>
@@ -2071,7 +2053,7 @@
         <v>81</v>
       </c>
       <c r="AL11" t="s">
-        <v>179</v>
+        <v>82</v>
       </c>
       <c r="AM11" t="s">
         <v>83</v>
@@ -2080,12 +2062,12 @@
         <v>84</v>
       </c>
       <c r="AO11" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="B12" t="s">
         <v>85</v>
@@ -2103,7 +2085,7 @@
         <v>89</v>
       </c>
       <c r="G12" t="s">
-        <v>182</v>
+        <v>90</v>
       </c>
       <c r="H12" t="s">
         <v>91</v>
@@ -2172,7 +2154,7 @@
         <v>63</v>
       </c>
       <c r="AD12" t="s">
-        <v>183</v>
+        <v>105</v>
       </c>
       <c r="AE12" t="s">
         <v>106</v>
@@ -2181,7 +2163,7 @@
         <v>67</v>
       </c>
       <c r="AG12" t="s">
-        <v>184</v>
+        <v>107</v>
       </c>
       <c r="AH12" t="s">
         <v>108</v>
@@ -2205,12 +2187,12 @@
         <v>111</v>
       </c>
       <c r="AO12" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B13" t="s">
         <v>113</v>
@@ -2255,7 +2237,7 @@
         <v>57</v>
       </c>
       <c r="P13" t="s">
-        <v>72</v>
+        <v>121</v>
       </c>
       <c r="Q13" t="s">
         <v>122</v>
@@ -2330,12 +2312,12 @@
         <v>132</v>
       </c>
       <c r="AO13" t="s">
-        <v>180</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="B14" t="s">
         <v>133</v>
@@ -2422,7 +2404,7 @@
         <v>63</v>
       </c>
       <c r="AD14" t="s">
-        <v>92</v>
+        <v>181</v>
       </c>
       <c r="AE14" t="s">
         <v>93</v>
@@ -2455,12 +2437,12 @@
         <v>144</v>
       </c>
       <c r="AO14" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>177</v>
+        <v>112</v>
       </c>
       <c r="B15" t="s">
         <v>145</v>
@@ -2487,7 +2469,7 @@
         <v>49</v>
       </c>
       <c r="J15" t="s">
-        <v>96</v>
+        <v>183</v>
       </c>
       <c r="K15" t="s">
         <v>97</v>
@@ -2505,7 +2487,7 @@
         <v>108</v>
       </c>
       <c r="P15" t="s">
-        <v>187</v>
+        <v>151</v>
       </c>
       <c r="Q15" t="s">
         <v>152</v>
@@ -2547,7 +2529,7 @@
         <v>156</v>
       </c>
       <c r="AD15" t="s">
-        <v>188</v>
+        <v>138</v>
       </c>
       <c r="AE15" t="s">
         <v>69</v>
@@ -2580,12 +2562,12 @@
         <v>159</v>
       </c>
       <c r="AO15" t="s">
-        <v>189</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B16" t="s">
         <v>160</v>
@@ -2624,7 +2606,7 @@
         <v>137</v>
       </c>
       <c r="N16" t="s">
-        <v>184</v>
+        <v>107</v>
       </c>
       <c r="O16" t="s">
         <v>108</v>
@@ -2672,7 +2654,7 @@
         <v>128</v>
       </c>
       <c r="AD16" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="AE16" t="s">
         <v>108</v>
@@ -2705,12 +2687,12 @@
         <v>169</v>
       </c>
       <c r="AO16" t="s">
-        <v>147</v>
+        <v>186</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="B17" t="s">
         <v>113</v>
@@ -2797,7 +2779,7 @@
         <v>173</v>
       </c>
       <c r="AD17" t="s">
-        <v>192</v>
+        <v>150</v>
       </c>
       <c r="AE17" t="s">
         <v>108</v>
@@ -2830,12 +2812,12 @@
         <v>175</v>
       </c>
       <c r="AO17" t="s">
-        <v>186</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>191</v>
+        <v>112</v>
       </c>
       <c r="B18" t="s">
         <v>42</v>
@@ -2862,7 +2844,7 @@
         <v>49</v>
       </c>
       <c r="J18" t="s">
-        <v>193</v>
+        <v>50</v>
       </c>
       <c r="K18" t="s">
         <v>51</v>
@@ -2880,7 +2862,7 @@
         <v>55</v>
       </c>
       <c r="P18" t="s">
-        <v>183</v>
+        <v>56</v>
       </c>
       <c r="Q18" t="s">
         <v>57</v>
@@ -2922,7 +2904,7 @@
         <v>63</v>
       </c>
       <c r="AD18" t="s">
-        <v>194</v>
+        <v>66</v>
       </c>
       <c r="AE18" t="s">
         <v>51</v>
@@ -2955,12 +2937,12 @@
         <v>73</v>
       </c>
       <c r="AO18" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B19" t="s">
         <v>42</v>
@@ -2999,7 +2981,7 @@
         <v>53</v>
       </c>
       <c r="N19" t="s">
-        <v>54</v>
+        <v>188</v>
       </c>
       <c r="O19" t="s">
         <v>55</v>
@@ -3080,12 +3062,12 @@
         <v>84</v>
       </c>
       <c r="AO19" t="s">
-        <v>180</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B20" t="s">
         <v>85</v>
@@ -3103,7 +3085,7 @@
         <v>89</v>
       </c>
       <c r="G20" t="s">
-        <v>90</v>
+        <v>190</v>
       </c>
       <c r="H20" t="s">
         <v>91</v>
@@ -3172,7 +3154,7 @@
         <v>63</v>
       </c>
       <c r="AD20" t="s">
-        <v>195</v>
+        <v>105</v>
       </c>
       <c r="AE20" t="s">
         <v>106</v>
@@ -3181,7 +3163,7 @@
         <v>67</v>
       </c>
       <c r="AG20" t="s">
-        <v>107</v>
+        <v>191</v>
       </c>
       <c r="AH20" t="s">
         <v>108</v>
@@ -3205,12 +3187,12 @@
         <v>111</v>
       </c>
       <c r="AO20" t="s">
-        <v>44</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>112</v>
+        <v>184</v>
       </c>
       <c r="B21" t="s">
         <v>113</v>
@@ -3330,12 +3312,12 @@
         <v>132</v>
       </c>
       <c r="AO21" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="B22" t="s">
         <v>133</v>
@@ -3353,7 +3335,7 @@
         <v>79</v>
       </c>
       <c r="G22" t="s">
-        <v>196</v>
+        <v>66</v>
       </c>
       <c r="H22" t="s">
         <v>51</v>
@@ -3455,12 +3437,12 @@
         <v>144</v>
       </c>
       <c r="AO22" t="s">
-        <v>115</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>177</v>
+        <v>41</v>
       </c>
       <c r="B23" t="s">
         <v>145</v>
@@ -3580,12 +3562,12 @@
         <v>159</v>
       </c>
       <c r="AO23" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>190</v>
+        <v>112</v>
       </c>
       <c r="B24" t="s">
         <v>160</v>
@@ -3603,7 +3585,7 @@
         <v>79</v>
       </c>
       <c r="G24" t="s">
-        <v>96</v>
+        <v>192</v>
       </c>
       <c r="H24" t="s">
         <v>97</v>
@@ -3681,7 +3663,7 @@
         <v>67</v>
       </c>
       <c r="AG24" t="s">
-        <v>167</v>
+        <v>193</v>
       </c>
       <c r="AH24" t="s">
         <v>83</v>
@@ -3705,12 +3687,12 @@
         <v>169</v>
       </c>
       <c r="AO24" t="s">
-        <v>197</v>
+        <v>162</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="B25" t="s">
         <v>113</v>
@@ -3830,12 +3812,12 @@
         <v>175</v>
       </c>
       <c r="AO25" t="s">
-        <v>198</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="B26" t="s">
         <v>42</v>
@@ -3874,13 +3856,13 @@
         <v>53</v>
       </c>
       <c r="N26" t="s">
-        <v>54</v>
+        <v>188</v>
       </c>
       <c r="O26" t="s">
         <v>55</v>
       </c>
       <c r="P26" t="s">
-        <v>183</v>
+        <v>56</v>
       </c>
       <c r="Q26" t="s">
         <v>57</v>
@@ -3931,7 +3913,7 @@
         <v>67</v>
       </c>
       <c r="AG26" t="s">
-        <v>68</v>
+        <v>194</v>
       </c>
       <c r="AH26" t="s">
         <v>69</v>
@@ -3955,12 +3937,12 @@
         <v>73</v>
       </c>
       <c r="AO26" t="s">
-        <v>147</v>
+        <v>186</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>191</v>
+        <v>41</v>
       </c>
       <c r="B27" t="s">
         <v>42</v>
@@ -3999,7 +3981,7 @@
         <v>53</v>
       </c>
       <c r="N27" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="O27" t="s">
         <v>55</v>
@@ -4047,7 +4029,7 @@
         <v>80</v>
       </c>
       <c r="AD27" t="s">
-        <v>54</v>
+        <v>195</v>
       </c>
       <c r="AE27" t="s">
         <v>55</v>
@@ -4080,12 +4062,12 @@
         <v>84</v>
       </c>
       <c r="AO27" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B28" t="s">
         <v>85</v>
@@ -4103,7 +4085,7 @@
         <v>89</v>
       </c>
       <c r="G28" t="s">
-        <v>187</v>
+        <v>90</v>
       </c>
       <c r="H28" t="s">
         <v>91</v>
@@ -4181,7 +4163,7 @@
         <v>67</v>
       </c>
       <c r="AG28" t="s">
-        <v>200</v>
+        <v>107</v>
       </c>
       <c r="AH28" t="s">
         <v>108</v>
@@ -4196,7 +4178,7 @@
         <v>72</v>
       </c>
       <c r="AL28" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="AM28" t="s">
         <v>108</v>
@@ -4205,12 +4187,12 @@
         <v>111</v>
       </c>
       <c r="AO28" t="s">
-        <v>87</v>
+        <v>147</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B29" t="s">
         <v>113</v>
@@ -4255,7 +4237,7 @@
         <v>57</v>
       </c>
       <c r="P29" t="s">
-        <v>121</v>
+        <v>195</v>
       </c>
       <c r="Q29" t="s">
         <v>122</v>
@@ -4330,12 +4312,12 @@
         <v>132</v>
       </c>
       <c r="AO29" t="s">
-        <v>87</v>
+        <v>186</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>190</v>
+        <v>41</v>
       </c>
       <c r="B30" t="s">
         <v>133</v>
@@ -4455,12 +4437,12 @@
         <v>144</v>
       </c>
       <c r="AO30" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="B31" t="s">
         <v>145</v>
@@ -4499,7 +4481,7 @@
         <v>95</v>
       </c>
       <c r="N31" t="s">
-        <v>150</v>
+        <v>195</v>
       </c>
       <c r="O31" t="s">
         <v>108</v>
@@ -4585,7 +4567,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>41</v>
+        <v>178</v>
       </c>
       <c r="B32" t="s">
         <v>160</v>
@@ -4630,7 +4612,7 @@
         <v>108</v>
       </c>
       <c r="P32" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="Q32" t="s">
         <v>83</v>
@@ -4672,7 +4654,7 @@
         <v>128</v>
       </c>
       <c r="AD32" t="s">
-        <v>166</v>
+        <v>199</v>
       </c>
       <c r="AE32" t="s">
         <v>108</v>
@@ -4696,7 +4678,7 @@
         <v>72</v>
       </c>
       <c r="AL32" t="s">
-        <v>201</v>
+        <v>167</v>
       </c>
       <c r="AM32" t="s">
         <v>83</v>
@@ -4705,12 +4687,12 @@
         <v>169</v>
       </c>
       <c r="AO32" t="s">
-        <v>87</v>
+        <v>162</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B33" t="s">
         <v>113</v>
@@ -4830,12 +4812,12 @@
         <v>175</v>
       </c>
       <c r="AO33" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B34" t="s">
         <v>42</v>
@@ -4853,7 +4835,7 @@
         <v>46</v>
       </c>
       <c r="G34" t="s">
-        <v>47</v>
+        <v>199</v>
       </c>
       <c r="H34" t="s">
         <v>48</v>
@@ -4931,7 +4913,7 @@
         <v>67</v>
       </c>
       <c r="AG34" t="s">
-        <v>187</v>
+        <v>68</v>
       </c>
       <c r="AH34" t="s">
         <v>69</v>
@@ -4955,12 +4937,12 @@
         <v>73</v>
       </c>
       <c r="AO34" t="s">
-        <v>115</v>
+        <v>186</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="B35" t="s">
         <v>42</v>
@@ -4978,7 +4960,7 @@
         <v>46</v>
       </c>
       <c r="G35" t="s">
-        <v>203</v>
+        <v>47</v>
       </c>
       <c r="H35" t="s">
         <v>48</v>
@@ -5005,7 +4987,7 @@
         <v>55</v>
       </c>
       <c r="P35" t="s">
-        <v>56</v>
+        <v>185</v>
       </c>
       <c r="Q35" t="s">
         <v>57</v>
@@ -5071,7 +5053,7 @@
         <v>81</v>
       </c>
       <c r="AL35" t="s">
-        <v>82</v>
+        <v>200</v>
       </c>
       <c r="AM35" t="s">
         <v>83</v>
@@ -5080,12 +5062,12 @@
         <v>84</v>
       </c>
       <c r="AO35" t="s">
-        <v>44</v>
+        <v>177</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>41</v>
+        <v>180</v>
       </c>
       <c r="B36" t="s">
         <v>85</v>
@@ -5103,7 +5085,7 @@
         <v>89</v>
       </c>
       <c r="G36" t="s">
-        <v>90</v>
+        <v>201</v>
       </c>
       <c r="H36" t="s">
         <v>91</v>
@@ -5124,13 +5106,13 @@
         <v>95</v>
       </c>
       <c r="N36" t="s">
-        <v>96</v>
+        <v>202</v>
       </c>
       <c r="O36" t="s">
         <v>97</v>
       </c>
       <c r="P36" t="s">
-        <v>204</v>
+        <v>98</v>
       </c>
       <c r="Q36" t="s">
         <v>99</v>
@@ -5205,7 +5187,7 @@
         <v>111</v>
       </c>
       <c r="AO36" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="37">
@@ -5228,7 +5210,7 @@
         <v>117</v>
       </c>
       <c r="G37" t="s">
-        <v>54</v>
+        <v>204</v>
       </c>
       <c r="H37" t="s">
         <v>55</v>
@@ -5255,7 +5237,7 @@
         <v>57</v>
       </c>
       <c r="P37" t="s">
-        <v>121</v>
+        <v>195</v>
       </c>
       <c r="Q37" t="s">
         <v>122</v>
@@ -5321,7 +5303,7 @@
         <v>131</v>
       </c>
       <c r="AL37" t="s">
-        <v>205</v>
+        <v>82</v>
       </c>
       <c r="AM37" t="s">
         <v>83</v>
@@ -5330,12 +5312,12 @@
         <v>132</v>
       </c>
       <c r="AO37" t="s">
-        <v>115</v>
+        <v>197</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="B38" t="s">
         <v>133</v>
@@ -5431,7 +5413,7 @@
         <v>67</v>
       </c>
       <c r="AG38" t="s">
-        <v>142</v>
+        <v>205</v>
       </c>
       <c r="AH38" t="s">
         <v>97</v>
@@ -5455,12 +5437,12 @@
         <v>144</v>
       </c>
       <c r="AO38" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>112</v>
+        <v>189</v>
       </c>
       <c r="B39" t="s">
         <v>145</v>
@@ -5499,7 +5481,7 @@
         <v>95</v>
       </c>
       <c r="N39" t="s">
-        <v>206</v>
+        <v>150</v>
       </c>
       <c r="O39" t="s">
         <v>108</v>
@@ -5571,7 +5553,7 @@
         <v>72</v>
       </c>
       <c r="AL39" t="s">
-        <v>207</v>
+        <v>157</v>
       </c>
       <c r="AM39" t="s">
         <v>83</v>
@@ -5580,12 +5562,12 @@
         <v>159</v>
       </c>
       <c r="AO39" t="s">
-        <v>189</v>
+        <v>115</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B40" t="s">
         <v>160</v>
@@ -5603,7 +5585,7 @@
         <v>79</v>
       </c>
       <c r="G40" t="s">
-        <v>208</v>
+        <v>96</v>
       </c>
       <c r="H40" t="s">
         <v>97</v>
@@ -5624,7 +5606,7 @@
         <v>137</v>
       </c>
       <c r="N40" t="s">
-        <v>209</v>
+        <v>107</v>
       </c>
       <c r="O40" t="s">
         <v>108</v>
@@ -5681,7 +5663,7 @@
         <v>67</v>
       </c>
       <c r="AG40" t="s">
-        <v>210</v>
+        <v>167</v>
       </c>
       <c r="AH40" t="s">
         <v>83</v>
@@ -5705,12 +5687,12 @@
         <v>169</v>
       </c>
       <c r="AO40" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="B41" t="s">
         <v>113</v>
@@ -5728,7 +5710,7 @@
         <v>117</v>
       </c>
       <c r="G41" t="s">
-        <v>211</v>
+        <v>54</v>
       </c>
       <c r="H41" t="s">
         <v>55</v>
@@ -5830,12 +5812,12 @@
         <v>175</v>
       </c>
       <c r="AO41" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>181</v>
+        <v>41</v>
       </c>
       <c r="B42" t="s">
         <v>42</v>
@@ -5862,7 +5844,7 @@
         <v>49</v>
       </c>
       <c r="J42" t="s">
-        <v>50</v>
+        <v>206</v>
       </c>
       <c r="K42" t="s">
         <v>51</v>
@@ -5874,13 +5856,13 @@
         <v>53</v>
       </c>
       <c r="N42" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="O42" t="s">
         <v>55</v>
       </c>
       <c r="P42" t="s">
-        <v>56</v>
+        <v>195</v>
       </c>
       <c r="Q42" t="s">
         <v>57</v>
@@ -5946,7 +5928,7 @@
         <v>72</v>
       </c>
       <c r="AL42" t="s">
-        <v>212</v>
+        <v>68</v>
       </c>
       <c r="AM42" t="s">
         <v>69</v>
@@ -5955,12 +5937,12 @@
         <v>73</v>
       </c>
       <c r="AO42" t="s">
-        <v>78</v>
+        <v>179</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="B43" t="s">
         <v>42</v>
@@ -5978,7 +5960,7 @@
         <v>46</v>
       </c>
       <c r="G43" t="s">
-        <v>213</v>
+        <v>47</v>
       </c>
       <c r="H43" t="s">
         <v>48</v>
@@ -6071,7 +6053,7 @@
         <v>81</v>
       </c>
       <c r="AL43" t="s">
-        <v>214</v>
+        <v>82</v>
       </c>
       <c r="AM43" t="s">
         <v>83</v>
@@ -6080,12 +6062,12 @@
         <v>84</v>
       </c>
       <c r="AO43" t="s">
-        <v>215</v>
+        <v>177</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="B44" t="s">
         <v>85</v>
@@ -6130,7 +6112,7 @@
         <v>97</v>
       </c>
       <c r="P44" t="s">
-        <v>98</v>
+        <v>207</v>
       </c>
       <c r="Q44" t="s">
         <v>99</v>
@@ -6196,7 +6178,7 @@
         <v>72</v>
       </c>
       <c r="AL44" t="s">
-        <v>201</v>
+        <v>107</v>
       </c>
       <c r="AM44" t="s">
         <v>108</v>
@@ -6205,12 +6187,12 @@
         <v>111</v>
       </c>
       <c r="AO44" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="B45" t="s">
         <v>113</v>
@@ -6249,7 +6231,7 @@
         <v>53</v>
       </c>
       <c r="N45" t="s">
-        <v>214</v>
+        <v>120</v>
       </c>
       <c r="O45" t="s">
         <v>57</v>
@@ -6321,7 +6303,7 @@
         <v>131</v>
       </c>
       <c r="AL45" t="s">
-        <v>82</v>
+        <v>209</v>
       </c>
       <c r="AM45" t="s">
         <v>83</v>
@@ -6330,12 +6312,12 @@
         <v>132</v>
       </c>
       <c r="AO45" t="s">
-        <v>115</v>
+        <v>179</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>181</v>
+        <v>112</v>
       </c>
       <c r="B46" t="s">
         <v>133</v>
@@ -6455,12 +6437,12 @@
         <v>144</v>
       </c>
       <c r="AO46" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="B47" t="s">
         <v>145</v>
@@ -6499,7 +6481,7 @@
         <v>95</v>
       </c>
       <c r="N47" t="s">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="O47" t="s">
         <v>108</v>
@@ -6556,7 +6538,7 @@
         <v>67</v>
       </c>
       <c r="AG47" t="s">
-        <v>157</v>
+        <v>199</v>
       </c>
       <c r="AH47" t="s">
         <v>83</v>
@@ -6580,12 +6562,12 @@
         <v>159</v>
       </c>
       <c r="AO47" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>181</v>
+        <v>41</v>
       </c>
       <c r="B48" t="s">
         <v>160</v>
@@ -6603,7 +6585,7 @@
         <v>79</v>
       </c>
       <c r="G48" t="s">
-        <v>96</v>
+        <v>211</v>
       </c>
       <c r="H48" t="s">
         <v>97</v>
@@ -6630,7 +6612,7 @@
         <v>108</v>
       </c>
       <c r="P48" t="s">
-        <v>216</v>
+        <v>82</v>
       </c>
       <c r="Q48" t="s">
         <v>83</v>
@@ -6696,7 +6678,7 @@
         <v>72</v>
       </c>
       <c r="AL48" t="s">
-        <v>72</v>
+        <v>167</v>
       </c>
       <c r="AM48" t="s">
         <v>83</v>
@@ -6705,12 +6687,12 @@
         <v>169</v>
       </c>
       <c r="AO48" t="s">
-        <v>215</v>
+        <v>162</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B49" t="s">
         <v>113</v>
@@ -6821,7 +6803,7 @@
         <v>174</v>
       </c>
       <c r="AL49" t="s">
-        <v>187</v>
+        <v>82</v>
       </c>
       <c r="AM49" t="s">
         <v>83</v>
@@ -6830,12 +6812,12 @@
         <v>175</v>
       </c>
       <c r="AO49" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B50" t="s">
         <v>42</v>
@@ -6853,7 +6835,7 @@
         <v>46</v>
       </c>
       <c r="G50" t="s">
-        <v>217</v>
+        <v>47</v>
       </c>
       <c r="H50" t="s">
         <v>48</v>
@@ -6955,12 +6937,12 @@
         <v>73</v>
       </c>
       <c r="AO50" t="s">
-        <v>180</v>
+        <v>78</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>41</v>
+        <v>198</v>
       </c>
       <c r="B51" t="s">
         <v>42</v>
@@ -7047,7 +7029,7 @@
         <v>80</v>
       </c>
       <c r="AD51" t="s">
-        <v>218</v>
+        <v>54</v>
       </c>
       <c r="AE51" t="s">
         <v>55</v>
@@ -7071,7 +7053,7 @@
         <v>81</v>
       </c>
       <c r="AL51" t="s">
-        <v>214</v>
+        <v>82</v>
       </c>
       <c r="AM51" t="s">
         <v>83</v>
@@ -7080,12 +7062,12 @@
         <v>84</v>
       </c>
       <c r="AO51" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B52" t="s">
         <v>85</v>
@@ -7103,7 +7085,7 @@
         <v>89</v>
       </c>
       <c r="G52" t="s">
-        <v>219</v>
+        <v>90</v>
       </c>
       <c r="H52" t="s">
         <v>91</v>
@@ -7112,7 +7094,7 @@
         <v>49</v>
       </c>
       <c r="J52" t="s">
-        <v>92</v>
+        <v>201</v>
       </c>
       <c r="K52" t="s">
         <v>93</v>
@@ -7196,7 +7178,7 @@
         <v>72</v>
       </c>
       <c r="AL52" t="s">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="AM52" t="s">
         <v>108</v>
@@ -7205,12 +7187,12 @@
         <v>111</v>
       </c>
       <c r="AO52" t="s">
-        <v>115</v>
+        <v>87</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B53" t="s">
         <v>113</v>
@@ -7228,7 +7210,7 @@
         <v>117</v>
       </c>
       <c r="G53" t="s">
-        <v>199</v>
+        <v>54</v>
       </c>
       <c r="H53" t="s">
         <v>55</v>
@@ -7330,12 +7312,12 @@
         <v>132</v>
       </c>
       <c r="AO53" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>190</v>
+        <v>112</v>
       </c>
       <c r="B54" t="s">
         <v>133</v>
@@ -7374,7 +7356,7 @@
         <v>137</v>
       </c>
       <c r="N54" t="s">
-        <v>96</v>
+        <v>199</v>
       </c>
       <c r="O54" t="s">
         <v>97</v>
@@ -7431,7 +7413,7 @@
         <v>67</v>
       </c>
       <c r="AG54" t="s">
-        <v>142</v>
+        <v>199</v>
       </c>
       <c r="AH54" t="s">
         <v>97</v>
@@ -7446,7 +7428,7 @@
         <v>72</v>
       </c>
       <c r="AL54" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="AM54" t="s">
         <v>97</v>
@@ -7455,7 +7437,7 @@
         <v>144</v>
       </c>
       <c r="AO54" t="s">
-        <v>189</v>
+        <v>78</v>
       </c>
     </row>
     <row r="55">
@@ -7487,7 +7469,7 @@
         <v>49</v>
       </c>
       <c r="J55" t="s">
-        <v>220</v>
+        <v>96</v>
       </c>
       <c r="K55" t="s">
         <v>97</v>
@@ -7499,7 +7481,7 @@
         <v>95</v>
       </c>
       <c r="N55" t="s">
-        <v>206</v>
+        <v>150</v>
       </c>
       <c r="O55" t="s">
         <v>108</v>
@@ -7547,7 +7529,7 @@
         <v>156</v>
       </c>
       <c r="AD55" t="s">
-        <v>138</v>
+        <v>212</v>
       </c>
       <c r="AE55" t="s">
         <v>69</v>
@@ -7556,7 +7538,7 @@
         <v>67</v>
       </c>
       <c r="AG55" t="s">
-        <v>72</v>
+        <v>157</v>
       </c>
       <c r="AH55" t="s">
         <v>83</v>
@@ -7580,12 +7562,12 @@
         <v>159</v>
       </c>
       <c r="AO55" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="B56" t="s">
         <v>160</v>
@@ -7612,7 +7594,7 @@
         <v>49</v>
       </c>
       <c r="J56" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="K56" t="s">
         <v>108</v>
@@ -7630,7 +7612,7 @@
         <v>108</v>
       </c>
       <c r="P56" t="s">
-        <v>216</v>
+        <v>82</v>
       </c>
       <c r="Q56" t="s">
         <v>83</v>
@@ -7705,12 +7687,12 @@
         <v>169</v>
       </c>
       <c r="AO56" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="B57" t="s">
         <v>113</v>
@@ -7749,7 +7731,7 @@
         <v>53</v>
       </c>
       <c r="N57" t="s">
-        <v>222</v>
+        <v>120</v>
       </c>
       <c r="O57" t="s">
         <v>57</v>
@@ -7830,12 +7812,12 @@
         <v>175</v>
       </c>
       <c r="AO57" t="s">
-        <v>115</v>
+        <v>186</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="B58" t="s">
         <v>42</v>
@@ -7946,7 +7928,7 @@
         <v>72</v>
       </c>
       <c r="AL58" t="s">
-        <v>68</v>
+        <v>214</v>
       </c>
       <c r="AM58" t="s">
         <v>69</v>
@@ -7955,12 +7937,12 @@
         <v>73</v>
       </c>
       <c r="AO58" t="s">
-        <v>202</v>
+        <v>78</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="B59" t="s">
         <v>42</v>
@@ -7987,7 +7969,7 @@
         <v>49</v>
       </c>
       <c r="J59" t="s">
-        <v>50</v>
+        <v>215</v>
       </c>
       <c r="K59" t="s">
         <v>51</v>
@@ -7999,7 +7981,7 @@
         <v>53</v>
       </c>
       <c r="N59" t="s">
-        <v>223</v>
+        <v>54</v>
       </c>
       <c r="O59" t="s">
         <v>55</v>
@@ -8080,12 +8062,12 @@
         <v>84</v>
       </c>
       <c r="AO59" t="s">
-        <v>162</v>
+        <v>203</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="B60" t="s">
         <v>85</v>
@@ -8112,7 +8094,7 @@
         <v>49</v>
       </c>
       <c r="J60" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="K60" t="s">
         <v>93</v>
@@ -8205,12 +8187,12 @@
         <v>111</v>
       </c>
       <c r="AO60" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>41</v>
+        <v>189</v>
       </c>
       <c r="B61" t="s">
         <v>113</v>
@@ -8249,7 +8231,7 @@
         <v>53</v>
       </c>
       <c r="N61" t="s">
-        <v>214</v>
+        <v>120</v>
       </c>
       <c r="O61" t="s">
         <v>57</v>
@@ -8321,7 +8303,7 @@
         <v>131</v>
       </c>
       <c r="AL61" t="s">
-        <v>201</v>
+        <v>82</v>
       </c>
       <c r="AM61" t="s">
         <v>83</v>
@@ -8330,12 +8312,12 @@
         <v>132</v>
       </c>
       <c r="AO61" t="s">
-        <v>147</v>
+        <v>197</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="B62" t="s">
         <v>133</v>
@@ -8374,7 +8356,7 @@
         <v>137</v>
       </c>
       <c r="N62" t="s">
-        <v>96</v>
+        <v>211</v>
       </c>
       <c r="O62" t="s">
         <v>97</v>
@@ -8431,7 +8413,7 @@
         <v>67</v>
       </c>
       <c r="AG62" t="s">
-        <v>142</v>
+        <v>195</v>
       </c>
       <c r="AH62" t="s">
         <v>97</v>
@@ -8455,12 +8437,12 @@
         <v>144</v>
       </c>
       <c r="AO62" t="s">
-        <v>147</v>
+        <v>208</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="B63" t="s">
         <v>145</v>
@@ -8478,7 +8460,7 @@
         <v>89</v>
       </c>
       <c r="G63" t="s">
-        <v>214</v>
+        <v>148</v>
       </c>
       <c r="H63" t="s">
         <v>51</v>
@@ -8547,7 +8529,7 @@
         <v>156</v>
       </c>
       <c r="AD63" t="s">
-        <v>138</v>
+        <v>202</v>
       </c>
       <c r="AE63" t="s">
         <v>69</v>
@@ -8556,7 +8538,7 @@
         <v>67</v>
       </c>
       <c r="AG63" t="s">
-        <v>72</v>
+        <v>157</v>
       </c>
       <c r="AH63" t="s">
         <v>83</v>
@@ -8580,12 +8562,12 @@
         <v>159</v>
       </c>
       <c r="AO63" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B64" t="s">
         <v>160</v>
@@ -8624,7 +8606,7 @@
         <v>137</v>
       </c>
       <c r="N64" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="O64" t="s">
         <v>108</v>
@@ -8705,12 +8687,12 @@
         <v>169</v>
       </c>
       <c r="AO64" t="s">
-        <v>78</v>
+        <v>182</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>112</v>
+        <v>180</v>
       </c>
       <c r="B65" t="s">
         <v>113</v>
@@ -8797,7 +8779,7 @@
         <v>173</v>
       </c>
       <c r="AD65" t="s">
-        <v>201</v>
+        <v>150</v>
       </c>
       <c r="AE65" t="s">
         <v>108</v>
@@ -8830,12 +8812,12 @@
         <v>175</v>
       </c>
       <c r="AO65" t="s">
-        <v>162</v>
+        <v>208</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>41</v>
+        <v>189</v>
       </c>
       <c r="B66" t="s">
         <v>42</v>
@@ -8955,12 +8937,12 @@
         <v>73</v>
       </c>
       <c r="AO66" t="s">
-        <v>44</v>
+        <v>187</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>112</v>
+        <v>178</v>
       </c>
       <c r="B67" t="s">
         <v>42</v>
@@ -8978,7 +8960,7 @@
         <v>46</v>
       </c>
       <c r="G67" t="s">
-        <v>47</v>
+        <v>218</v>
       </c>
       <c r="H67" t="s">
         <v>48</v>
@@ -8987,7 +8969,7 @@
         <v>49</v>
       </c>
       <c r="J67" t="s">
-        <v>201</v>
+        <v>50</v>
       </c>
       <c r="K67" t="s">
         <v>51</v>
@@ -8999,7 +8981,7 @@
         <v>53</v>
       </c>
       <c r="N67" t="s">
-        <v>201</v>
+        <v>54</v>
       </c>
       <c r="O67" t="s">
         <v>55</v>
@@ -9047,7 +9029,7 @@
         <v>80</v>
       </c>
       <c r="AD67" t="s">
-        <v>54</v>
+        <v>204</v>
       </c>
       <c r="AE67" t="s">
         <v>55</v>
@@ -9071,7 +9053,7 @@
         <v>81</v>
       </c>
       <c r="AL67" t="s">
-        <v>82</v>
+        <v>219</v>
       </c>
       <c r="AM67" t="s">
         <v>83</v>
@@ -9080,12 +9062,12 @@
         <v>84</v>
       </c>
       <c r="AO67" t="s">
-        <v>215</v>
+        <v>182</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>112</v>
+        <v>189</v>
       </c>
       <c r="B68" t="s">
         <v>85</v>
@@ -9103,7 +9085,7 @@
         <v>89</v>
       </c>
       <c r="G68" t="s">
-        <v>90</v>
+        <v>220</v>
       </c>
       <c r="H68" t="s">
         <v>91</v>
@@ -9112,7 +9094,7 @@
         <v>49</v>
       </c>
       <c r="J68" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="K68" t="s">
         <v>93</v>
@@ -9130,7 +9112,7 @@
         <v>97</v>
       </c>
       <c r="P68" t="s">
-        <v>98</v>
+        <v>207</v>
       </c>
       <c r="Q68" t="s">
         <v>99</v>
@@ -9196,7 +9178,7 @@
         <v>72</v>
       </c>
       <c r="AL68" t="s">
-        <v>200</v>
+        <v>107</v>
       </c>
       <c r="AM68" t="s">
         <v>108</v>
@@ -9210,7 +9192,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B69" t="s">
         <v>113</v>
@@ -9297,7 +9279,7 @@
         <v>128</v>
       </c>
       <c r="AD69" t="s">
-        <v>96</v>
+        <v>185</v>
       </c>
       <c r="AE69" t="s">
         <v>97</v>
@@ -9330,12 +9312,12 @@
         <v>132</v>
       </c>
       <c r="AO69" t="s">
-        <v>78</v>
+        <v>208</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B70" t="s">
         <v>133</v>
@@ -9455,12 +9437,12 @@
         <v>144</v>
       </c>
       <c r="AO70" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B71" t="s">
         <v>145</v>
@@ -9499,13 +9481,13 @@
         <v>95</v>
       </c>
       <c r="N71" t="s">
-        <v>150</v>
+        <v>221</v>
       </c>
       <c r="O71" t="s">
         <v>108</v>
       </c>
       <c r="P71" t="s">
-        <v>151</v>
+        <v>222</v>
       </c>
       <c r="Q71" t="s">
         <v>152</v>
@@ -9580,12 +9562,12 @@
         <v>159</v>
       </c>
       <c r="AO71" t="s">
-        <v>78</v>
+        <v>187</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="B72" t="s">
         <v>160</v>
@@ -9672,7 +9654,7 @@
         <v>128</v>
       </c>
       <c r="AD72" t="s">
-        <v>225</v>
+        <v>166</v>
       </c>
       <c r="AE72" t="s">
         <v>108</v>
@@ -9696,7 +9678,7 @@
         <v>72</v>
       </c>
       <c r="AL72" t="s">
-        <v>214</v>
+        <v>167</v>
       </c>
       <c r="AM72" t="s">
         <v>83</v>
@@ -9710,7 +9692,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>176</v>
+        <v>112</v>
       </c>
       <c r="B73" t="s">
         <v>113</v>
@@ -9830,12 +9812,12 @@
         <v>175</v>
       </c>
       <c r="AO73" t="s">
-        <v>78</v>
+        <v>177</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B74" t="s">
         <v>42</v>
@@ -9853,7 +9835,7 @@
         <v>46</v>
       </c>
       <c r="G74" t="s">
-        <v>47</v>
+        <v>199</v>
       </c>
       <c r="H74" t="s">
         <v>48</v>
@@ -9955,12 +9937,12 @@
         <v>73</v>
       </c>
       <c r="AO74" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="B75" t="s">
         <v>42</v>
@@ -9987,7 +9969,7 @@
         <v>49</v>
       </c>
       <c r="J75" t="s">
-        <v>50</v>
+        <v>223</v>
       </c>
       <c r="K75" t="s">
         <v>51</v>
@@ -10080,12 +10062,12 @@
         <v>84</v>
       </c>
       <c r="AO75" t="s">
-        <v>202</v>
+        <v>78</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B76" t="s">
         <v>85</v>
@@ -10205,12 +10187,12 @@
         <v>111</v>
       </c>
       <c r="AO76" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B77" t="s">
         <v>113</v>
@@ -10330,12 +10312,12 @@
         <v>132</v>
       </c>
       <c r="AO77" t="s">
-        <v>162</v>
+        <v>187</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="B78" t="s">
         <v>133</v>
@@ -10362,7 +10344,7 @@
         <v>49</v>
       </c>
       <c r="J78" t="s">
-        <v>183</v>
+        <v>54</v>
       </c>
       <c r="K78" t="s">
         <v>55</v>
@@ -10380,7 +10362,7 @@
         <v>97</v>
       </c>
       <c r="P78" t="s">
-        <v>183</v>
+        <v>138</v>
       </c>
       <c r="Q78" t="s">
         <v>69</v>
@@ -10422,7 +10404,7 @@
         <v>63</v>
       </c>
       <c r="AD78" t="s">
-        <v>226</v>
+        <v>92</v>
       </c>
       <c r="AE78" t="s">
         <v>93</v>
@@ -10431,7 +10413,7 @@
         <v>67</v>
       </c>
       <c r="AG78" t="s">
-        <v>227</v>
+        <v>142</v>
       </c>
       <c r="AH78" t="s">
         <v>97</v>
@@ -10455,12 +10437,12 @@
         <v>144</v>
       </c>
       <c r="AO78" t="s">
-        <v>44</v>
+        <v>187</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="B79" t="s">
         <v>145</v>
@@ -10547,7 +10529,7 @@
         <v>156</v>
       </c>
       <c r="AD79" t="s">
-        <v>228</v>
+        <v>138</v>
       </c>
       <c r="AE79" t="s">
         <v>69</v>
@@ -10580,12 +10562,12 @@
         <v>159</v>
       </c>
       <c r="AO79" t="s">
-        <v>229</v>
+        <v>203</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="B80" t="s">
         <v>160</v>
@@ -10612,7 +10594,7 @@
         <v>49</v>
       </c>
       <c r="J80" t="s">
-        <v>207</v>
+        <v>150</v>
       </c>
       <c r="K80" t="s">
         <v>108</v>
@@ -10696,7 +10678,7 @@
         <v>72</v>
       </c>
       <c r="AL80" t="s">
-        <v>167</v>
+        <v>224</v>
       </c>
       <c r="AM80" t="s">
         <v>83</v>
@@ -10705,12 +10687,12 @@
         <v>169</v>
       </c>
       <c r="AO80" t="s">
-        <v>229</v>
+        <v>147</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="B81" t="s">
         <v>113</v>
@@ -10749,7 +10731,7 @@
         <v>53</v>
       </c>
       <c r="N81" t="s">
-        <v>230</v>
+        <v>120</v>
       </c>
       <c r="O81" t="s">
         <v>57</v>
@@ -10830,7 +10812,7 @@
         <v>175</v>
       </c>
       <c r="AO81" t="s">
-        <v>44</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>
